--- a/docassemble/StudentEvaluations/data/sources/massachusetts_entire_student_record_request_es.xlsx
+++ b/docassemble/StudentEvaluations/data/sources/massachusetts_entire_student_record_request_es.xlsx
@@ -23831,7 +23831,7 @@
           <t xml:space="preserve">Antes de comenzar, necesitará:
  1. Nombre completo y fecha de nacimiento de su hijo/a.
  2. Nombre y correo electrónico del director de la escuela de su hijo/a.
- 3. Si su hijo/a tiene un ${iep}, nombre y correo electrónico del contacto de educación especial.
+ 3. Si su hijo/a tiene un {IEP}, nombre y correo electrónico del contacto de educación especial.
  Puede encontrar la información del director en el sitio web de la escuela. El nombre del contacto de educación especial debería aparecer en el IEP de su hijo/a. También puede llamar a la escuela de su hijo/a para solicitar esta información.
  Si necesita ayuda para encontrar algún dato, comuníquese con la línea de ayuda de MAC al 617-357-8431. También puede enviar un mensaje [aquí.] (https://www.massadvocates.org/helpline)
 </t>
